--- a/Test/TestResult_5_5_3_4_3_1_CRP_2Stage_MIP_5_RQMC_42_Q_S_1_0_AE_NoC_Re-solve_10_1_0.xlsx
+++ b/Test/TestResult_5_5_3_4_3_1_CRP_2Stage_MIP_5_RQMC_42_Q_S_1_0_AE_NoC_Re-solve_10_1_0.xlsx
@@ -1016,7 +1016,7 @@
         <v>19030.87120849909</v>
       </c>
       <c r="H2" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -1085,7 +1085,7 @@
         <v>2</v>
       </c>
       <c r="AE2" t="n">
-        <v>4.348626613616943</v>
+        <v>6.173351049423218</v>
       </c>
     </row>
   </sheetData>
